--- a/signaalin_esikäsittely.xlsx
+++ b/signaalin_esikäsittely.xlsx
@@ -1,21 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30502"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ja\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\KURSSIT\Digitaalilaitteiden suunnittelu\Projekti\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77" documentId="11_B79980F77C593E13EF33DC7F2971FC481A11BB50" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E062FE56-32A0-4E24-A592-E81F3B7C66A5}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="11880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="11880"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <r>
       <t>T(</t>
@@ -179,17 +181,17 @@
     <t>R7=-Uout/(Ur4-Ur5)*R4</t>
   </si>
   <si>
-    <t>R6</t>
+    <t>sisäänmenojännite(mV)</t>
   </si>
   <si>
-    <t>R7</t>
+    <t>ulostulojännite(V)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -254,6 +256,1900 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.34744444444444444"/>
+          <c:y val="2.7777777777777776E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>[1]Sheet1!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ulostulojännite(V)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>[1]Sheet1!$A$2:$A$62</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="61"/>
+                <c:pt idx="0">
+                  <c:v>-300</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-290</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-280</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-270</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-260</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-250</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-240</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-230</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-220</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-210</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-200</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-190</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-180</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-170</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-160</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-150</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-140</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-130</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-120</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-110</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-100</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-90</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-80</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-70</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>-60</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>-50</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>-40</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>-30</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>-20</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>-10</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>190</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>210</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>220</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>230</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>240</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>260</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>270</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>280</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>290</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>300</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>[1]Sheet1!$B$2:$B$62</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="61"/>
+                <c:pt idx="0">
+                  <c:v>3.08</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.04</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.95</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.9</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.85</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.79</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.75</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.7</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.66</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.58</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.5299999999999998</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.48</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.4300000000000002</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.39</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.34</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.29</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.25</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2.2000000000000002</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2.15</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2.09</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2.04</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1.99</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1.94</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1.9</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1.84</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1.8</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1.75</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1.71</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1.65</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1.61</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1.49</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1.43</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1.39</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1.34</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1.3</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1.24</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1.2</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1.1499999999999999</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1.1000000000000001</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1.05</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.99</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.93</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.89</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.61</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.56000000000000005</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.48</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.44</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.39</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.34</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.28999999999999998</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.24</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.15</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.05</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E75F-495E-B1F1-C2AE9E81510C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="808065487"/>
+        <c:axId val="808074223"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="808065487"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="300"/>
+          <c:min val="-300"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                    <a:effectLst/>
+                  </a:rPr>
+                  <a:t>sisäänmenojännite(mV)</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+                  <a:t> </a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="808074223"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="808074223"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="3"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                    <a:effectLst/>
+                  </a:rPr>
+                  <a:t>ulostulojännite(V)</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+                  <a:t> </a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="808065487"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1348153</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>ulostulojännite(V)</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="A2">
+            <v>-300</v>
+          </cell>
+          <cell r="B2">
+            <v>3.08</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3">
+            <v>-290</v>
+          </cell>
+          <cell r="B3">
+            <v>3.04</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4">
+            <v>-280</v>
+          </cell>
+          <cell r="B4">
+            <v>3</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5">
+            <v>-270</v>
+          </cell>
+          <cell r="B5">
+            <v>2.95</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6">
+            <v>-260</v>
+          </cell>
+          <cell r="B6">
+            <v>2.9</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7">
+            <v>-250</v>
+          </cell>
+          <cell r="B7">
+            <v>2.85</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8">
+            <v>-240</v>
+          </cell>
+          <cell r="B8">
+            <v>2.79</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9">
+            <v>-230</v>
+          </cell>
+          <cell r="B9">
+            <v>2.75</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10">
+            <v>-220</v>
+          </cell>
+          <cell r="B10">
+            <v>2.7</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11">
+            <v>-210</v>
+          </cell>
+          <cell r="B11">
+            <v>2.66</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12">
+            <v>-200</v>
+          </cell>
+          <cell r="B12">
+            <v>2.58</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13">
+            <v>-190</v>
+          </cell>
+          <cell r="B13">
+            <v>2.5299999999999998</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14">
+            <v>-180</v>
+          </cell>
+          <cell r="B14">
+            <v>2.48</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15">
+            <v>-170</v>
+          </cell>
+          <cell r="B15">
+            <v>2.4300000000000002</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16">
+            <v>-160</v>
+          </cell>
+          <cell r="B16">
+            <v>2.39</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17">
+            <v>-150</v>
+          </cell>
+          <cell r="B17">
+            <v>2.34</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="A18">
+            <v>-140</v>
+          </cell>
+          <cell r="B18">
+            <v>2.29</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="A19">
+            <v>-130</v>
+          </cell>
+          <cell r="B19">
+            <v>2.25</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="A20">
+            <v>-120</v>
+          </cell>
+          <cell r="B20">
+            <v>2.2000000000000002</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="A21">
+            <v>-110</v>
+          </cell>
+          <cell r="B21">
+            <v>2.15</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="A22">
+            <v>-100</v>
+          </cell>
+          <cell r="B22">
+            <v>2.09</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="A23">
+            <v>-90</v>
+          </cell>
+          <cell r="B23">
+            <v>2.04</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="A24">
+            <v>-80</v>
+          </cell>
+          <cell r="B24">
+            <v>1.99</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="A25">
+            <v>-70</v>
+          </cell>
+          <cell r="B25">
+            <v>1.94</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="A26">
+            <v>-60</v>
+          </cell>
+          <cell r="B26">
+            <v>1.9</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="A27">
+            <v>-50</v>
+          </cell>
+          <cell r="B27">
+            <v>1.84</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="A28">
+            <v>-40</v>
+          </cell>
+          <cell r="B28">
+            <v>1.8</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="A29">
+            <v>-30</v>
+          </cell>
+          <cell r="B29">
+            <v>1.75</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="A30">
+            <v>-20</v>
+          </cell>
+          <cell r="B30">
+            <v>1.71</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="A31">
+            <v>-10</v>
+          </cell>
+          <cell r="B31">
+            <v>1.65</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="A32">
+            <v>0</v>
+          </cell>
+          <cell r="B32">
+            <v>1.61</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="A33">
+            <v>10</v>
+          </cell>
+          <cell r="B33">
+            <v>1.49</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="A34">
+            <v>20</v>
+          </cell>
+          <cell r="B34">
+            <v>1.43</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="A35">
+            <v>30</v>
+          </cell>
+          <cell r="B35">
+            <v>1.39</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="A36">
+            <v>40</v>
+          </cell>
+          <cell r="B36">
+            <v>1.34</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="A37">
+            <v>50</v>
+          </cell>
+          <cell r="B37">
+            <v>1.3</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="A38">
+            <v>60</v>
+          </cell>
+          <cell r="B38">
+            <v>1.24</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="A39">
+            <v>70</v>
+          </cell>
+          <cell r="B39">
+            <v>1.2</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="A40">
+            <v>80</v>
+          </cell>
+          <cell r="B40">
+            <v>1.1499999999999999</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="A41">
+            <v>90</v>
+          </cell>
+          <cell r="B41">
+            <v>1.1000000000000001</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="A42">
+            <v>100</v>
+          </cell>
+          <cell r="B42">
+            <v>1.05</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="A43">
+            <v>110</v>
+          </cell>
+          <cell r="B43">
+            <v>0.99</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="A44">
+            <v>120</v>
+          </cell>
+          <cell r="B44">
+            <v>0.93</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="A45">
+            <v>130</v>
+          </cell>
+          <cell r="B45">
+            <v>0.89</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="A46">
+            <v>140</v>
+          </cell>
+          <cell r="B46">
+            <v>0.85</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="A47">
+            <v>150</v>
+          </cell>
+          <cell r="B47">
+            <v>0.8</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="A48">
+            <v>160</v>
+          </cell>
+          <cell r="B48">
+            <v>0.75</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="A49">
+            <v>170</v>
+          </cell>
+          <cell r="B49">
+            <v>0.7</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="A50">
+            <v>180</v>
+          </cell>
+          <cell r="B50">
+            <v>0.65</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="A51">
+            <v>190</v>
+          </cell>
+          <cell r="B51">
+            <v>0.61</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="A52">
+            <v>200</v>
+          </cell>
+          <cell r="B52">
+            <v>0.56000000000000005</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="A53">
+            <v>210</v>
+          </cell>
+          <cell r="B53">
+            <v>0.48</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="A54">
+            <v>220</v>
+          </cell>
+          <cell r="B54">
+            <v>0.44</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="A55">
+            <v>230</v>
+          </cell>
+          <cell r="B55">
+            <v>0.39</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="A56">
+            <v>240</v>
+          </cell>
+          <cell r="B56">
+            <v>0.34</v>
+          </cell>
+        </row>
+        <row r="57">
+          <cell r="A57">
+            <v>250</v>
+          </cell>
+          <cell r="B57">
+            <v>0.28999999999999998</v>
+          </cell>
+        </row>
+        <row r="58">
+          <cell r="A58">
+            <v>260</v>
+          </cell>
+          <cell r="B58">
+            <v>0.24</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="A59">
+            <v>270</v>
+          </cell>
+          <cell r="B59">
+            <v>0.2</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="A60">
+            <v>280</v>
+          </cell>
+          <cell r="B60">
+            <v>0.15</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="A61">
+            <v>290</v>
+          </cell>
+          <cell r="B61">
+            <v>0.1</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="A62">
+            <v>300</v>
+          </cell>
+          <cell r="B62">
+            <v>0.05</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -518,16 +2414,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L16"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L80"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.5703125" customWidth="1"/>
+    <col min="1" max="1" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21" customWidth="1"/>
     <col min="8" max="8" width="25.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -547,141 +2444,623 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
-      <c r="A2">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3">
         <v>-30</v>
       </c>
-      <c r="B2">
+      <c r="B3">
         <v>30</v>
       </c>
-      <c r="D2">
+      <c r="D3">
         <v>10</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G3" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="K2">
+      <c r="K3">
         <f>-(-12)/(50*10^-6)</f>
         <v>240000.00000000003</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="18">
-      <c r="A3" s="2" t="s">
+    <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D4" t="s">
         <v>10</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G4" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K3">
+      <c r="K4">
         <f>0.3*10000/(12-0.3)</f>
         <v>256.41025641025641</v>
       </c>
-      <c r="L3">
+      <c r="L4">
         <v>256</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="1">
-        <f>A2*$D$2</f>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <f>A3*$D$3</f>
         <v>-300</v>
       </c>
-      <c r="B4" s="1">
-        <f>B2*$D$2</f>
+      <c r="B5" s="1">
+        <f>B3*$D$3</f>
         <v>300</v>
       </c>
-      <c r="D4">
+      <c r="D5">
         <v>12</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H5" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
-      <c r="A5" t="s">
+    <row r="6" spans="1:12" ht="18" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H6" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
-      <c r="A6">
-        <f>$D$4/(0.00005)</f>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <f>$D$5/(0.00005)</f>
         <v>240000</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="H7" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
-      <c r="H7" s="3" t="s">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H8" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
-      <c r="H8" s="3" t="s">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H9" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
-      <c r="G9" t="s">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
         <v>19</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="H10" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="K9">
+      <c r="K10">
         <f>-3/(-0.3-0.3)*10000</f>
         <v>50000</v>
       </c>
-      <c r="L9" t="s">
+      <c r="L10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
-      <c r="H10" s="3" t="s">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H11" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
-      <c r="H11" s="3" t="s">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H12" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
-      <c r="H12" s="3" t="s">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H13" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
-      <c r="A14" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="A15" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="16" spans="1:12">
-      <c r="A16" t="s">
+      <c r="B19" t="s">
         <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>-300</v>
+      </c>
+      <c r="B20">
+        <v>3.08</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>-290</v>
+      </c>
+      <c r="B21">
+        <v>3.04</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>-280</v>
+      </c>
+      <c r="B22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>-270</v>
+      </c>
+      <c r="B23">
+        <v>2.95</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>-260</v>
+      </c>
+      <c r="B24">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>-250</v>
+      </c>
+      <c r="B25">
+        <v>2.85</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>-240</v>
+      </c>
+      <c r="B26">
+        <v>2.79</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>-230</v>
+      </c>
+      <c r="B27">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>-220</v>
+      </c>
+      <c r="B28">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>-210</v>
+      </c>
+      <c r="B29">
+        <v>2.66</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>-200</v>
+      </c>
+      <c r="B30">
+        <v>2.58</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>-190</v>
+      </c>
+      <c r="B31">
+        <v>2.5299999999999998</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>-180</v>
+      </c>
+      <c r="B32">
+        <v>2.48</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>-170</v>
+      </c>
+      <c r="B33">
+        <v>2.4300000000000002</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>-160</v>
+      </c>
+      <c r="B34">
+        <v>2.39</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>-150</v>
+      </c>
+      <c r="B35">
+        <v>2.34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>-140</v>
+      </c>
+      <c r="B36">
+        <v>2.29</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>-130</v>
+      </c>
+      <c r="B37">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>-120</v>
+      </c>
+      <c r="B38">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>-110</v>
+      </c>
+      <c r="B39">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>-100</v>
+      </c>
+      <c r="B40">
+        <v>2.09</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>-90</v>
+      </c>
+      <c r="B41">
+        <v>2.04</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>-80</v>
+      </c>
+      <c r="B42">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>-70</v>
+      </c>
+      <c r="B43">
+        <v>1.94</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>-60</v>
+      </c>
+      <c r="B44">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>-50</v>
+      </c>
+      <c r="B45">
+        <v>1.84</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>-40</v>
+      </c>
+      <c r="B46">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>-30</v>
+      </c>
+      <c r="B47">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>-20</v>
+      </c>
+      <c r="B48">
+        <v>1.71</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>-10</v>
+      </c>
+      <c r="B49">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>0</v>
+      </c>
+      <c r="B50">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>10</v>
+      </c>
+      <c r="B51">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>20</v>
+      </c>
+      <c r="B52">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>30</v>
+      </c>
+      <c r="B53">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>40</v>
+      </c>
+      <c r="B54">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>50</v>
+      </c>
+      <c r="B55">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>60</v>
+      </c>
+      <c r="B56">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>70</v>
+      </c>
+      <c r="B57">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>80</v>
+      </c>
+      <c r="B58">
+        <v>1.1499999999999999</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>90</v>
+      </c>
+      <c r="B59">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>100</v>
+      </c>
+      <c r="B60">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>110</v>
+      </c>
+      <c r="B61">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>120</v>
+      </c>
+      <c r="B62">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>130</v>
+      </c>
+      <c r="B63">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>140</v>
+      </c>
+      <c r="B64">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>150</v>
+      </c>
+      <c r="B65">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>160</v>
+      </c>
+      <c r="B66">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>170</v>
+      </c>
+      <c r="B67">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>180</v>
+      </c>
+      <c r="B68">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>190</v>
+      </c>
+      <c r="B69">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>200</v>
+      </c>
+      <c r="B70">
+        <v>0.56000000000000005</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>210</v>
+      </c>
+      <c r="B71">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>220</v>
+      </c>
+      <c r="B72">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>230</v>
+      </c>
+      <c r="B73">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>240</v>
+      </c>
+      <c r="B74">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>250</v>
+      </c>
+      <c r="B75">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>260</v>
+      </c>
+      <c r="B76">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>270</v>
+      </c>
+      <c r="B77">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>280</v>
+      </c>
+      <c r="B78">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>290</v>
+      </c>
+      <c r="B79">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>300</v>
+      </c>
+      <c r="B80">
+        <v>0.05</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>